--- a/Project/Media Control/CreateTicket/data/create-ticket-cases.xlsx
+++ b/Project/Media Control/CreateTicket/data/create-ticket-cases.xlsx
@@ -1,83 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sajjaporn.su\Desktop\my-playwright-test\Project\Media Control\CreateTicket\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462F736C-79AF-4C33-B754-952AB43200B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Cases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>Client</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>Package</t>
-  </si>
-  <si>
-    <t>DurationMinutes</t>
-  </si>
-  <si>
-    <t>DurationSeconds</t>
-  </si>
-  <si>
-    <t>MaterialLink</t>
-  </si>
-  <si>
-    <t>BriefLink</t>
-  </si>
-  <si>
-    <t>PlanBTV_80Red (Plan B TV)</t>
-  </si>
-  <si>
-    <t>https://example.com/sheet-a-material.jpg</t>
-  </si>
-  <si>
-    <t>https://example.com/sheet-a-brief.pdf</t>
-  </si>
-  <si>
-    <t>SAWASDEE</t>
-  </si>
-  <si>
-    <t>MILO</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -110,14 +72,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -442,51 +396,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="15.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.3828125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.4609375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Client</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Product</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Package</v>
+      </c>
+      <c r="D1" t="str">
+        <v>DurationMinutes</v>
+      </c>
+      <c r="E1" t="str">
+        <v>DurationSeconds</v>
+      </c>
+      <c r="F1" t="str">
+        <v>MaterialLink</v>
+      </c>
+      <c r="G1" t="str">
+        <v>BriefLink</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Auto Add 1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Auto Add 1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>7-Eleven Plus (QATEST)</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -494,20 +438,39 @@
       <c r="E2">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
+      <c r="F2" t="str">
+        <v>https://example.com/sheet-a-material.jpg</v>
+      </c>
+      <c r="G2" t="str">
+        <v>https://example.com/sheet-a-brief.pdf</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.3"/>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Auto Add 2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Auto Add 2</v>
+      </c>
+      <c r="C3" t="str">
+        <v>7-Eleven Plus (QATEST)</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>20</v>
+      </c>
+      <c r="F3" t="str">
+        <v>https://example.com/sheet-b-material.jpg</v>
+      </c>
+      <c r="G3" t="str">
+        <v>https://example.com/sheet-b-brief.pdf</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G1 C2 E2:G2" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>